--- a/scm/backend/app/assets/TemplateBulkUpload.xlsx
+++ b/scm/backend/app/assets/TemplateBulkUpload.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Parts" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Parts" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,10 +28,25 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B71C1C"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -39,7 +55,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFF3E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00B71C1C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFEFEF"/>
       </patternFill>
     </fill>
   </fills>
@@ -55,9 +81,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -132,6 +163,63 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Template Guide</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Choose ONE mode for this entire sheet: Counting, Defect Detection, or Measurement. Every part row below is uploaded under this mode — there is no per-row mode column.</t>
+      </text>
+    </comment>
+    <comment ref="A3" authorId="0" shapeId="0">
+      <text>
+        <t>REQUIRED. Unique identifier for this part (e.g. BOLT-001).
+Duplicate part_code rows are skipped on upload.</t>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0" shapeId="0">
+      <text>
+        <t>Display name of the part. Falls back to part_code if left blank.</t>
+      </text>
+    </comment>
+    <comment ref="C3" authorId="0" shapeId="0">
+      <text>
+        <t>Groups this part under a category. Auto-created if new.
+Grouping/filtering only — does not select or load any model.</t>
+      </text>
+    </comment>
+    <comment ref="D3" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. Leave blank unless your process embeds an image reference here.</t>
+      </text>
+    </comment>
+    <comment ref="E3" authorId="0" shapeId="0">
+      <text>
+        <t>Weight of the part, in grams. One fixed number — no min/max, no instances.</t>
+      </text>
+    </comment>
+    <comment ref="AF3" authorId="0" shapeId="0">
+      <text>
+        <t>true/false — whether this geometric check applies.</t>
+      </text>
+    </comment>
+    <comment ref="AG3" authorId="0" shapeId="0">
+      <text>
+        <t>true/false — whether this geometric check applies.</t>
+      </text>
+    </comment>
+    <comment ref="AH3" authorId="0" shapeId="0">
+      <text>
+        <t>true/false — whether this geometric check applies.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -423,291 +511,612 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG2"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="17" customWidth="1" min="14" max="14"/>
-    <col width="17" customWidth="1" min="15" max="15"/>
-    <col width="21" customWidth="1" min="16" max="16"/>
-    <col width="25" customWidth="1" min="17" max="17"/>
-    <col width="25" customWidth="1" min="18" max="18"/>
-    <col width="21" customWidth="1" min="19" max="19"/>
-    <col width="25" customWidth="1" min="20" max="20"/>
-    <col width="25" customWidth="1" min="21" max="21"/>
-    <col width="16" customWidth="1" min="22" max="22"/>
-    <col width="16" customWidth="1" min="23" max="23"/>
-    <col width="16" customWidth="1" min="24" max="24"/>
-    <col width="18" customWidth="1" min="25" max="25"/>
-    <col width="22" customWidth="1" min="26" max="26"/>
-    <col width="22" customWidth="1" min="27" max="27"/>
-    <col width="16" customWidth="1" min="28" max="28"/>
-    <col width="17" customWidth="1" min="29" max="29"/>
-    <col width="17" customWidth="1" min="30" max="30"/>
-    <col width="19" customWidth="1" min="31" max="31"/>
-    <col width="18" customWidth="1" min="32" max="32"/>
-    <col width="20" customWidth="1" min="33" max="33"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="78" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>How to fill this template</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Step 1 — Set the mode ONCE for the whole sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>On the 'Parts' sheet, cell B1 sets the mode for every part in this file:</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Counting, Defect Detection, or Measurement (pick from the dropdown).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>There is no per-row mode column — every row is uploaded under this one mode.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>To upload parts for a different mode, use a separate file with a different B1 value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Fixed Columns</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>What it means</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>part_code</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>REQUIRED. Unique ID for the part. Duplicates are skipped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>part_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Display name. Defaults to part_code if left blank.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>category_name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>model_name</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Groups the part under a category. Auto-created if new.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>image</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Optional. Leave blank unless your process embeds an image reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>part_weight</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>part_length</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>part_length_min</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>part_length_max</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>part_width</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>part_width_min</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>part_width_max</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>part_height</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>part_height_min</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>part_height_max</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>part_inner_diameter</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>part_inner_diameter_min</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>part_inner_diameter_max</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>part_outer_diameter</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>part_outer_diameter_min</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>part_outer_diameter_max</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>part_angle</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>part_angle_min</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>part_angle_max</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>part_arch_length</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>part_arch_length_min</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>part_arch_length_max</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>part_sector</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>part_sector_min</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>part_sector_max</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Weight in grams. One fixed number — no min/max, no instances.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>part_co_planarity</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>true/false.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>part_parallelity</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>true/false.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>part_concentricity</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>BOLT-001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>M8 Bolt</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Fasteners</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>bolt</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="G2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H2" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="I2" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="J2" t="n">
-        <v>8</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="n">
-        <v>40</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="n">
-        <v>8</v>
-      </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>false</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>true/false.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Dimension Parameters (length, width, height, id, od, angle, arch, sector)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Each family supports UNLIMITED numbered instances (length1, length2, ...).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  length1 = nominal value, length1_min / length1_max = tolerance (optional).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Add more by adding columns yourself: length2, length2_min, length2_max, etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>'id' = inner diameter, 'od' = outer diameter, 'arch' = arch length.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Defects</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>d1_name is one defect. Add more the same way: d2_name, d3_name, etc.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="14" customWidth="1" min="29" max="29"/>
+    <col width="14" customWidth="1" min="30" max="30"/>
+    <col width="14" customWidth="1" min="31" max="31"/>
+    <col width="19" customWidth="1" min="32" max="32"/>
+    <col width="18" customWidth="1" min="33" max="33"/>
+    <col width="20" customWidth="1" min="34" max="34"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Mode of Operation for this sheet:</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Counting</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>part_code</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>part_name</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>category_name</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>part_weight</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>length1</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>length1_min</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>length1_max</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>width1</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>width1_min</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>width1_max</t>
+        </is>
+      </c>
+      <c r="L3" s="6" t="inlineStr">
+        <is>
+          <t>height1</t>
+        </is>
+      </c>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>height1_min</t>
+        </is>
+      </c>
+      <c r="N3" s="6" t="inlineStr">
+        <is>
+          <t>height1_max</t>
+        </is>
+      </c>
+      <c r="O3" s="6" t="inlineStr">
+        <is>
+          <t>id1</t>
+        </is>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>id1_min</t>
+        </is>
+      </c>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>id1_max</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>od1</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>od1_min</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>od1_max</t>
+        </is>
+      </c>
+      <c r="U3" s="6" t="inlineStr">
+        <is>
+          <t>angle1</t>
+        </is>
+      </c>
+      <c r="V3" s="6" t="inlineStr">
+        <is>
+          <t>angle1_min</t>
+        </is>
+      </c>
+      <c r="W3" s="6" t="inlineStr">
+        <is>
+          <t>angle1_max</t>
+        </is>
+      </c>
+      <c r="X3" s="6" t="inlineStr">
+        <is>
+          <t>arch1</t>
+        </is>
+      </c>
+      <c r="Y3" s="6" t="inlineStr">
+        <is>
+          <t>arch1_min</t>
+        </is>
+      </c>
+      <c r="Z3" s="6" t="inlineStr">
+        <is>
+          <t>arch1_max</t>
+        </is>
+      </c>
+      <c r="AA3" s="6" t="inlineStr">
+        <is>
+          <t>sector1</t>
+        </is>
+      </c>
+      <c r="AB3" s="6" t="inlineStr">
+        <is>
+          <t>sector1_min</t>
+        </is>
+      </c>
+      <c r="AC3" s="6" t="inlineStr">
+        <is>
+          <t>sector1_max</t>
+        </is>
+      </c>
+      <c r="AD3" s="6" t="inlineStr">
+        <is>
+          <t>d1_name</t>
+        </is>
+      </c>
+      <c r="AE3" s="6" t="inlineStr">
+        <is>
+          <t>d2_name</t>
+        </is>
+      </c>
+      <c r="AF3" s="6" t="inlineStr">
+        <is>
+          <t>part_co_planarity</t>
+        </is>
+      </c>
+      <c r="AG3" s="6" t="inlineStr">
+        <is>
+          <t>part_parallelity</t>
+        </is>
+      </c>
+      <c r="AH3" s="6" t="inlineStr">
+        <is>
+          <t>part_concentricity</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BOLT-001</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>M8 Bolt</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Fasteners</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>40</v>
+      </c>
+      <c r="G4" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="n">
+        <v>8</v>
+      </c>
+      <c r="S4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="T4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>WASHER-002</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>M8 Washer</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Fasteners</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="P5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="R5" t="n">
+        <v>16</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="T5" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Counting,Defect Detection,Measurement"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
 </file>